--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C968"/>
+  <dimension ref="A1:C971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -12160,20 +12160,53 @@
       </c>
     </row>
     <row r="968" customFormat="1" s="1">
-      <c r="B968" t="inlineStr">
+      <c r="B968" s="0" t="inlineStr">
         <is>
           <t>スマスロスーパーリオエース2</t>
         </is>
       </c>
-      <c r="C968" t="inlineStr">
+      <c r="C968" s="0" t="inlineStr">
         <is>
           <t>リオエース2</t>
         </is>
       </c>
     </row>
-    <row r="969" customFormat="1" s="1"/>
-    <row r="970" customFormat="1" s="1"/>
-    <row r="971" customFormat="1" s="1"/>
+    <row r="969" customFormat="1" s="1">
+      <c r="B969" s="0" t="inlineStr">
+        <is>
+          <t>パチスロ ダンジョンに出会いを求めるのは間違っているだろうか2</t>
+        </is>
+      </c>
+      <c r="C969" s="0" t="inlineStr">
+        <is>
+          <t>ダンまち2</t>
+        </is>
+      </c>
+    </row>
+    <row r="970" customFormat="1" s="1">
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>忍魂参 〜奥義皆伝ノ章〜</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>忍魂参</t>
+        </is>
+      </c>
+    </row>
+    <row r="971" customFormat="1" s="1">
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>スマスロ ゲゲゲの鬼太郎 覚醒</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>ゲゲゲの鬼太郎 覚醒</t>
+        </is>
+      </c>
+    </row>
     <row r="972" customFormat="1" s="1"/>
     <row r="973" customFormat="1" s="1"/>
     <row r="974" customFormat="1" s="1"/>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C971"/>
+  <dimension ref="A1:C974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -12184,32 +12184,65 @@
       </c>
     </row>
     <row r="970" customFormat="1" s="1">
-      <c r="B970" t="inlineStr">
+      <c r="B970" s="0" t="inlineStr">
         <is>
           <t>忍魂参 〜奥義皆伝ノ章〜</t>
         </is>
       </c>
-      <c r="C970" t="inlineStr">
+      <c r="C970" s="0" t="inlineStr">
         <is>
           <t>忍魂参</t>
         </is>
       </c>
     </row>
     <row r="971" customFormat="1" s="1">
-      <c r="B971" t="inlineStr">
+      <c r="B971" s="0" t="inlineStr">
         <is>
           <t>スマスロ ゲゲゲの鬼太郎 覚醒</t>
         </is>
       </c>
-      <c r="C971" t="inlineStr">
+      <c r="C971" s="0" t="inlineStr">
         <is>
           <t>ゲゲゲの鬼太郎 覚醒</t>
         </is>
       </c>
     </row>
-    <row r="972" customFormat="1" s="1"/>
-    <row r="973" customFormat="1" s="1"/>
-    <row r="974" customFormat="1" s="1"/>
+    <row r="972" customFormat="1" s="1">
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>L戦国乙女5 業火を穿つ宿焔の双刃</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>戦国乙女5</t>
+        </is>
+      </c>
+    </row>
+    <row r="973" customFormat="1" s="1">
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>スロット ソードアート・オンラインII</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>SAOII</t>
+        </is>
+      </c>
+    </row>
+    <row r="974" customFormat="1" s="1">
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>スマスロ BIRDIE WING -Golf Girls' Story-</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>BIRDIE WING</t>
+        </is>
+      </c>
+    </row>
     <row r="975" customFormat="1" s="1"/>
     <row r="976" customFormat="1" s="1"/>
     <row r="977" customFormat="1" s="1"/>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C974"/>
+  <dimension ref="A1:C1005"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -12208,72 +12208,413 @@
       </c>
     </row>
     <row r="972" customFormat="1" s="1">
-      <c r="B972" t="inlineStr">
+      <c r="B972" s="0" t="inlineStr">
         <is>
           <t>L戦国乙女5 業火を穿つ宿焔の双刃</t>
         </is>
       </c>
-      <c r="C972" t="inlineStr">
+      <c r="C972" s="0" t="inlineStr">
         <is>
           <t>戦国乙女5</t>
         </is>
       </c>
     </row>
     <row r="973" customFormat="1" s="1">
-      <c r="B973" t="inlineStr">
+      <c r="B973" s="0" t="inlineStr">
         <is>
           <t>スロット ソードアート・オンラインII</t>
         </is>
       </c>
-      <c r="C973" t="inlineStr">
+      <c r="C973" s="0" t="inlineStr">
         <is>
           <t>SAOII</t>
         </is>
       </c>
     </row>
     <row r="974" customFormat="1" s="1">
-      <c r="B974" t="inlineStr">
+      <c r="B974" s="0" t="inlineStr">
         <is>
           <t>スマスロ BIRDIE WING -Golf Girls' Story-</t>
         </is>
       </c>
-      <c r="C974" t="inlineStr">
+      <c r="C974" s="0" t="inlineStr">
         <is>
           <t>BIRDIE WING</t>
         </is>
       </c>
     </row>
-    <row r="975" customFormat="1" s="1"/>
-    <row r="976" customFormat="1" s="1"/>
-    <row r="977" customFormat="1" s="1"/>
-    <row r="978" customFormat="1" s="1"/>
-    <row r="979" customFormat="1" s="1"/>
-    <row r="980" customFormat="1" s="1"/>
-    <row r="981" customFormat="1" s="1"/>
-    <row r="982" customFormat="1" s="1"/>
-    <row r="983" customFormat="1" s="1"/>
-    <row r="984" customFormat="1" s="1"/>
-    <row r="985" customFormat="1" s="1"/>
-    <row r="986" customFormat="1" s="1"/>
-    <row r="987" customFormat="1" s="1"/>
-    <row r="988" customFormat="1" s="1"/>
-    <row r="989" customFormat="1" s="1"/>
-    <row r="990" customFormat="1" s="1"/>
-    <row r="991" customFormat="1" s="1"/>
-    <row r="992" customFormat="1" s="1"/>
-    <row r="993" customFormat="1" s="1"/>
-    <row r="994" customFormat="1" s="1"/>
-    <row r="995" customFormat="1" s="1"/>
-    <row r="996" customFormat="1" s="1"/>
-    <row r="997" customFormat="1" s="1"/>
-    <row r="998" customFormat="1" s="1"/>
-    <row r="999" customFormat="1" s="1"/>
-    <row r="1000" customFormat="1" s="1"/>
-    <row r="1001" customFormat="1" s="1"/>
-    <row r="1002" customFormat="1" s="1"/>
-    <row r="1003" customFormat="1" s="1"/>
-    <row r="1004" customFormat="1" s="1"/>
-    <row r="1005" customFormat="1" s="1"/>
+    <row r="975" customFormat="1" s="1">
+      <c r="B975" s="0" t="inlineStr">
+        <is>
+          <t>SハッピージャグラーVIII</t>
+        </is>
+      </c>
+      <c r="C975" s="0" t="inlineStr">
+        <is>
+          <t>ハピジャグV</t>
+        </is>
+      </c>
+    </row>
+    <row r="976" customFormat="1" s="1">
+      <c r="B976" s="0" t="inlineStr">
+        <is>
+          <t>L無職転生NM</t>
+        </is>
+      </c>
+      <c r="C976" s="0" t="inlineStr">
+        <is>
+          <t>無職転生</t>
+        </is>
+      </c>
+    </row>
+    <row r="977" customFormat="1" s="1">
+      <c r="B977" s="0" t="inlineStr">
+        <is>
+          <t>マジカルハロウィンボーナストリガ</t>
+        </is>
+      </c>
+      <c r="C977" s="0" t="inlineStr">
+        <is>
+          <t>LBマジハロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="978" customFormat="1" s="1">
+      <c r="B978" s="0" t="inlineStr">
+        <is>
+          <t>クレアの秘宝伝ボーナストリガー</t>
+        </is>
+      </c>
+      <c r="C978" s="0" t="inlineStr">
+        <is>
+          <t>クレアの秘宝伝</t>
+        </is>
+      </c>
+    </row>
+    <row r="979" customFormat="1" s="1">
+      <c r="B979" s="0" t="inlineStr">
+        <is>
+          <t>LBシェイクボーナストリガーA1</t>
+        </is>
+      </c>
+      <c r="C979" s="0" t="inlineStr">
+        <is>
+          <t>LBシェイク</t>
+        </is>
+      </c>
+    </row>
+    <row r="980" customFormat="1" s="1">
+      <c r="B980" s="0" t="inlineStr">
+        <is>
+          <t>ミリオンゴッド-神々の軌跡-</t>
+        </is>
+      </c>
+      <c r="C980" s="0" t="inlineStr">
+        <is>
+          <t>ゴッド神々の軌跡</t>
+        </is>
+      </c>
+    </row>
+    <row r="981" customFormat="1" s="1">
+      <c r="B981" s="0" t="inlineStr">
+        <is>
+          <t>異世界かるてっとBT</t>
+        </is>
+      </c>
+      <c r="C981" s="0" t="inlineStr">
+        <is>
+          <t>異世界かるてっと</t>
+        </is>
+      </c>
+    </row>
+    <row r="982" customFormat="1" s="1">
+      <c r="B982" s="0" t="inlineStr">
+        <is>
+          <t>L革命機ヴァルヴレイヴ2jF</t>
+        </is>
+      </c>
+      <c r="C982" s="0" t="inlineStr">
+        <is>
+          <t>ヴァルヴレイヴ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="983" customFormat="1" s="1">
+      <c r="B983" s="0" t="inlineStr">
+        <is>
+          <t>スマスロ マギアレコード</t>
+        </is>
+      </c>
+      <c r="C983" s="0" t="inlineStr">
+        <is>
+          <t>マギレコ</t>
+        </is>
+      </c>
+    </row>
+    <row r="984" customFormat="1" s="1">
+      <c r="B984" s="0" t="inlineStr">
+        <is>
+          <t>Lガンダムユニコーン2jA</t>
+        </is>
+      </c>
+      <c r="C984" s="0" t="inlineStr">
+        <is>
+          <t>ユニコーン覚醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="985" customFormat="1" s="1">
+      <c r="B985" s="0" t="inlineStr">
+        <is>
+          <t>スマスロ ビッグドリーム</t>
+        </is>
+      </c>
+      <c r="C985" s="0" t="inlineStr">
+        <is>
+          <t>ビッグドリーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="986" customFormat="1" s="1">
+      <c r="B986" s="0" t="inlineStr">
+        <is>
+          <t>ゴッドイーター リザレクション</t>
+        </is>
+      </c>
+      <c r="C986" s="0" t="inlineStr">
+        <is>
+          <t>ゴッドイーター</t>
+        </is>
+      </c>
+    </row>
+    <row r="987" customFormat="1" s="1">
+      <c r="B987" s="0" t="inlineStr">
+        <is>
+          <t>L新鬼武者3SA</t>
+        </is>
+      </c>
+      <c r="C987" s="0" t="inlineStr">
+        <is>
+          <t>新鬼武者3</t>
+        </is>
+      </c>
+    </row>
+    <row r="988" customFormat="1" s="1">
+      <c r="B988" s="0" t="inlineStr">
+        <is>
+          <t>ディスクアップULTRARMIX</t>
+        </is>
+      </c>
+      <c r="C988" s="0" t="inlineStr">
+        <is>
+          <t>ディスクアップUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="989" customFormat="1" s="1">
+      <c r="B989" s="0" t="inlineStr">
+        <is>
+          <t>パチスロ 戦国恋姫</t>
+        </is>
+      </c>
+      <c r="C989" s="0" t="inlineStr">
+        <is>
+          <t>戦国恋姫</t>
+        </is>
+      </c>
+    </row>
+    <row r="990" customFormat="1" s="1">
+      <c r="B990" s="0" t="inlineStr">
+        <is>
+          <t>反逆のルルーシュ3 CC&amp;カレン</t>
+        </is>
+      </c>
+      <c r="C990" s="0" t="inlineStr">
+        <is>
+          <t>ギアス3C.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="991" customFormat="1" s="1">
+      <c r="B991" s="0" t="inlineStr">
+        <is>
+          <t>この素晴らしい世界に祝福を!</t>
+        </is>
+      </c>
+      <c r="C991" s="0" t="inlineStr">
+        <is>
+          <t>このすば</t>
+        </is>
+      </c>
+    </row>
+    <row r="992" customFormat="1" s="1">
+      <c r="B992" s="0" t="inlineStr">
+        <is>
+          <t>エウレカハイエボゼロART</t>
+        </is>
+      </c>
+      <c r="C992" s="0" t="inlineStr">
+        <is>
+          <t>エウレカART</t>
+        </is>
+      </c>
+    </row>
+    <row r="993" customFormat="1" s="1">
+      <c r="B993" s="0" t="inlineStr">
+        <is>
+          <t>スマスロ防振り</t>
+        </is>
+      </c>
+      <c r="C993" s="0" t="inlineStr">
+        <is>
+          <t>防振り</t>
+        </is>
+      </c>
+    </row>
+    <row r="994" customFormat="1" s="1">
+      <c r="B994" s="0" t="inlineStr">
+        <is>
+          <t>甲鉄城のカバネリ 海門決戦</t>
+        </is>
+      </c>
+      <c r="C994" s="0" t="inlineStr">
+        <is>
+          <t>カバネリ海門決戦</t>
+        </is>
+      </c>
+    </row>
+    <row r="995" customFormat="1" s="1">
+      <c r="B995" s="0" t="inlineStr">
+        <is>
+          <t>バジリスク絆2天膳 BLACK</t>
+        </is>
+      </c>
+      <c r="C995" s="0" t="inlineStr">
+        <is>
+          <t>バジ絆2天膳</t>
+        </is>
+      </c>
+    </row>
+    <row r="996" customFormat="1" s="1">
+      <c r="B996" s="0" t="inlineStr">
+        <is>
+          <t>Lラブ嬢3Wご指名はいかがですか</t>
+        </is>
+      </c>
+      <c r="C996" s="0" t="inlineStr">
+        <is>
+          <t>ラブ嬢3</t>
+        </is>
+      </c>
+    </row>
+    <row r="997" customFormat="1" s="1">
+      <c r="B997" s="0" t="inlineStr">
+        <is>
+          <t>スマスロ ニューキングハナハナV</t>
+        </is>
+      </c>
+      <c r="C997" s="0" t="inlineStr">
+        <is>
+          <t>スマートキンハナV</t>
+        </is>
+      </c>
+    </row>
+    <row r="998" customFormat="1" s="1">
+      <c r="B998" s="0" t="inlineStr">
+        <is>
+          <t>沖ドキ!DUO アンコール</t>
+        </is>
+      </c>
+      <c r="C998" s="0" t="inlineStr">
+        <is>
+          <t>L沖ドキDUO</t>
+        </is>
+      </c>
+    </row>
+    <row r="999" customFormat="1" s="1">
+      <c r="B999" s="0" t="inlineStr">
+        <is>
+          <t>Lソードアート・オンラインII</t>
+        </is>
+      </c>
+      <c r="C999" s="0" t="inlineStr">
+        <is>
+          <t>SAOII</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000" customFormat="1" s="1">
+      <c r="B1000" s="0" t="inlineStr">
+        <is>
+          <t>L戦国乙女5</t>
+        </is>
+      </c>
+      <c r="C1000" s="0" t="inlineStr">
+        <is>
+          <t>戦国乙女5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001" customFormat="1" s="1">
+      <c r="B1001" s="0" t="inlineStr">
+        <is>
+          <t>L BIRDIE WING</t>
+        </is>
+      </c>
+      <c r="C1001" s="0" t="inlineStr">
+        <is>
+          <t>BIRDIE WING</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002" customFormat="1" s="1">
+      <c r="B1002" s="0" t="inlineStr">
+        <is>
+          <t>ハードボイルド</t>
+        </is>
+      </c>
+      <c r="C1002" s="0" t="inlineStr">
+        <is>
+          <t>ハードボイルド</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003" customFormat="1" s="1">
+      <c r="B1003" s="0" t="inlineStr">
+        <is>
+          <t>幼女戦記</t>
+        </is>
+      </c>
+      <c r="C1003" s="0" t="inlineStr">
+        <is>
+          <t>幼女戦記</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004" customFormat="1" s="1">
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>L忍魂参 奥義皆伝ノ章</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>忍魂参</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005" customFormat="1" s="1">
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Lゲゲゲの鬼太郎 覚醒</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>ゲゲゲの鬼太郎 覚醒</t>
+        </is>
+      </c>
+    </row>
     <row r="1006" customFormat="1" s="1"/>
     <row r="1007" customFormat="1" s="1"/>
     <row r="1008" customFormat="1" s="1"/>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1005"/>
+  <dimension ref="A1:C1007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -12592,31 +12592,53 @@
       </c>
     </row>
     <row r="1004" customFormat="1" s="1">
-      <c r="B1004" t="inlineStr">
+      <c r="B1004" s="0" t="inlineStr">
         <is>
           <t>L忍魂参 奥義皆伝ノ章</t>
         </is>
       </c>
-      <c r="C1004" t="inlineStr">
+      <c r="C1004" s="0" t="inlineStr">
         <is>
           <t>忍魂参</t>
         </is>
       </c>
     </row>
     <row r="1005" customFormat="1" s="1">
-      <c r="B1005" t="inlineStr">
+      <c r="B1005" s="0" t="inlineStr">
         <is>
           <t>Lゲゲゲの鬼太郎 覚醒</t>
         </is>
       </c>
-      <c r="C1005" t="inlineStr">
+      <c r="C1005" s="0" t="inlineStr">
         <is>
           <t>ゲゲゲの鬼太郎 覚醒</t>
         </is>
       </c>
     </row>
-    <row r="1006" customFormat="1" s="1"/>
-    <row r="1007" customFormat="1" s="1"/>
+    <row r="1006" customFormat="1" s="1">
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>スマスロ BIRDIE WING</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>BIRDIE WING</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007" customFormat="1" s="1">
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>LソードアートオンラインIIPA1</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>SAOII</t>
+        </is>
+      </c>
+    </row>
     <row r="1008" customFormat="1" s="1"/>
     <row r="1009" customFormat="1" s="1"/>
     <row r="1010" customFormat="1" s="1"/>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1007"/>
+  <dimension ref="A1:C1015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -12616,37 +12616,125 @@
       </c>
     </row>
     <row r="1006" customFormat="1" s="1">
-      <c r="B1006" t="inlineStr">
+      <c r="B1006" s="0" t="inlineStr">
         <is>
           <t>スマスロ BIRDIE WING</t>
         </is>
       </c>
-      <c r="C1006" t="inlineStr">
+      <c r="C1006" s="0" t="inlineStr">
         <is>
           <t>BIRDIE WING</t>
         </is>
       </c>
     </row>
     <row r="1007" customFormat="1" s="1">
-      <c r="B1007" t="inlineStr">
+      <c r="B1007" s="0" t="inlineStr">
         <is>
           <t>LソードアートオンラインIIPA1</t>
         </is>
       </c>
-      <c r="C1007" t="inlineStr">
+      <c r="C1007" s="0" t="inlineStr">
         <is>
           <t>SAOII</t>
         </is>
       </c>
     </row>
-    <row r="1008" customFormat="1" s="1"/>
-    <row r="1009" customFormat="1" s="1"/>
-    <row r="1010" customFormat="1" s="1"/>
-    <row r="1011" customFormat="1" s="1"/>
-    <row r="1012" customFormat="1" s="1"/>
-    <row r="1013" customFormat="1" s="1"/>
-    <row r="1014" customFormat="1" s="1"/>
-    <row r="1015" customFormat="1" s="1"/>
+    <row r="1008" customFormat="1" s="1">
+      <c r="B1008" s="0" t="inlineStr">
+        <is>
+          <t>L SAO2</t>
+        </is>
+      </c>
+      <c r="C1008" s="0" t="inlineStr">
+        <is>
+          <t>SAOII</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009" customFormat="1" s="1">
+      <c r="B1009" s="0" t="inlineStr">
+        <is>
+          <t>Lミリオンゴッド</t>
+        </is>
+      </c>
+      <c r="C1009" s="0" t="inlineStr">
+        <is>
+          <t>ゴッド神々の軌跡</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010" customFormat="1" s="1">
+      <c r="B1010" s="0" t="inlineStr">
+        <is>
+          <t>スマスロ北斗</t>
+        </is>
+      </c>
+      <c r="C1010" s="0" t="inlineStr">
+        <is>
+          <t>スマスロ北斗の拳</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011" customFormat="1" s="1">
+      <c r="B1011" s="0" t="inlineStr">
+        <is>
+          <t>Lドッチ</t>
+        </is>
+      </c>
+      <c r="C1011" s="0" t="inlineStr">
+        <is>
+          <t>アニスロドッチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012" customFormat="1" s="1">
+      <c r="B1012" s="0" t="inlineStr">
+        <is>
+          <t>Lユニコーン2</t>
+        </is>
+      </c>
+      <c r="C1012" s="0" t="inlineStr">
+        <is>
+          <t>ユニコーン覚醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013" customFormat="1" s="1">
+      <c r="B1013" s="0" t="inlineStr">
+        <is>
+          <t>L鏡</t>
+        </is>
+      </c>
+      <c r="C1013" s="0" t="inlineStr">
+        <is>
+          <t>エリサラ鏡</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014" customFormat="1" s="1">
+      <c r="B1014" s="0" t="inlineStr">
+        <is>
+          <t>このすば</t>
+        </is>
+      </c>
+      <c r="C1014" s="0" t="inlineStr">
+        <is>
+          <t>このすば</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015" customFormat="1" s="1">
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>沖ドキGOLD</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>沖ドキGOLD30</t>
+        </is>
+      </c>
+    </row>
     <row r="1016" customFormat="1" s="1"/>
     <row r="1017" customFormat="1" s="1"/>
     <row r="1018" customFormat="1" s="1"/>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -1523,7 +1523,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ダークネス8.7</t>
+          <t>ToLOVEるトランス</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>ダークネス8.7</t>
+          <t>ToLOVEるトランス</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>ToLOVEるダークネス</t>
+          <t>ToLOVEる</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>ダークネス8.7</t>
+          <t>ToLOVEるトランス</t>
         </is>
       </c>
     </row>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>ダークネス8.7</t>
+          <t>ToLOVEるトランス</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lデビクラ5</t>
+          <t>デビクラ5</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lデビクラ5</t>
+          <t>デビクラ5</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Lデビクラ5</t>
+          <t>デビクラ5</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Lデビクラ5</t>
+          <t>デビクラ5</t>
         </is>
       </c>
     </row>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1049"/>
+  <dimension ref="A1:C1069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -13120,49 +13120,269 @@
       </c>
     </row>
     <row r="1048" customFormat="1" s="1">
-      <c r="B1048" t="inlineStr">
+      <c r="B1048" s="0" t="inlineStr">
         <is>
           <t>L ひぐらしのなく頃に 業</t>
         </is>
       </c>
-      <c r="C1048" t="inlineStr">
+      <c r="C1048" s="0" t="inlineStr">
         <is>
           <t>ひぐらし業</t>
         </is>
       </c>
     </row>
     <row r="1049" customFormat="1" s="1">
-      <c r="B1049" t="inlineStr">
+      <c r="B1049" s="0" t="inlineStr">
         <is>
           <t>Lひぐらしのなく頃に業</t>
         </is>
       </c>
-      <c r="C1049" t="inlineStr">
+      <c r="C1049" s="0" t="inlineStr">
         <is>
           <t>ひぐらし業</t>
         </is>
       </c>
     </row>
-    <row r="1050" customFormat="1" s="1"/>
-    <row r="1051" customFormat="1" s="1"/>
-    <row r="1052" customFormat="1" s="1"/>
-    <row r="1053" customFormat="1" s="1"/>
-    <row r="1054" customFormat="1" s="1"/>
-    <row r="1055" customFormat="1" s="1"/>
-    <row r="1056" customFormat="1" s="1"/>
-    <row r="1057" customFormat="1" s="1"/>
-    <row r="1058" customFormat="1" s="1"/>
-    <row r="1059" customFormat="1" s="1"/>
-    <row r="1060" customFormat="1" s="1"/>
-    <row r="1061" customFormat="1" s="1"/>
-    <row r="1062" customFormat="1" s="1"/>
-    <row r="1063" customFormat="1" s="1"/>
-    <row r="1064" customFormat="1" s="1"/>
-    <row r="1065" customFormat="1" s="1"/>
-    <row r="1066" customFormat="1" s="1"/>
-    <row r="1067" customFormat="1" s="1"/>
-    <row r="1068" customFormat="1" s="1"/>
-    <row r="1069" customFormat="1" s="1"/>
+    <row r="1050" customFormat="1" s="1">
+      <c r="B1050" s="0" t="inlineStr">
+        <is>
+          <t>Lアリフレタ職業デ世界最強</t>
+        </is>
+      </c>
+      <c r="C1050" s="0" t="inlineStr">
+        <is>
+          <t>あり職</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051" customFormat="1" s="1">
+      <c r="B1051" s="0" t="inlineStr">
+        <is>
+          <t>L犬夜叉2</t>
+        </is>
+      </c>
+      <c r="C1051" s="0" t="inlineStr">
+        <is>
+          <t>犬夜叉2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052" customFormat="1" s="1">
+      <c r="B1052" s="0" t="inlineStr">
+        <is>
+          <t>スマスロワンパンマン</t>
+        </is>
+      </c>
+      <c r="C1052" s="0" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053" customFormat="1" s="1">
+      <c r="B1053" s="0" t="inlineStr">
+        <is>
+          <t>スマスロ やじきた道中記参る!</t>
+        </is>
+      </c>
+      <c r="C1053" s="0" t="inlineStr">
+        <is>
+          <t>やじきた</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054" customFormat="1" s="1">
+      <c r="B1054" s="0" t="inlineStr">
+        <is>
+          <t>スマスロ ストリートファイター6</t>
+        </is>
+      </c>
+      <c r="C1054" s="0" t="inlineStr">
+        <is>
+          <t>スト6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055" customFormat="1" s="1">
+      <c r="B1055" s="0" t="inlineStr">
+        <is>
+          <t>スロット ワールドダイスター</t>
+        </is>
+      </c>
+      <c r="C1055" s="0" t="inlineStr">
+        <is>
+          <t>ワールドダイスター</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056" customFormat="1" s="1">
+      <c r="B1056" s="0" t="inlineStr">
+        <is>
+          <t>L邪神ちゃんドロップキック</t>
+        </is>
+      </c>
+      <c r="C1056" s="0" t="inlineStr">
+        <is>
+          <t>邪神ちゃん</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057" customFormat="1" s="1">
+      <c r="B1057" s="0" t="inlineStr">
+        <is>
+          <t>スマスロ とんでもスキルで異世界放浪メシ</t>
+        </is>
+      </c>
+      <c r="C1057" s="0" t="inlineStr">
+        <is>
+          <t>とんスキ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058" customFormat="1" s="1">
+      <c r="B1058" s="0" t="inlineStr">
+        <is>
+          <t>Lやじきた道中記参る!</t>
+        </is>
+      </c>
+      <c r="C1058" s="0" t="inlineStr">
+        <is>
+          <t>やじきた</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059" customFormat="1" s="1">
+      <c r="B1059" s="0" t="inlineStr">
+        <is>
+          <t>Lストリートファイター6</t>
+        </is>
+      </c>
+      <c r="C1059" s="0" t="inlineStr">
+        <is>
+          <t>スト6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060" customFormat="1" s="1">
+      <c r="B1060" s="0" t="inlineStr">
+        <is>
+          <t>Lとある魔術の禁書目録2</t>
+        </is>
+      </c>
+      <c r="C1060" s="0" t="inlineStr">
+        <is>
+          <t>とある禁書目録2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061" customFormat="1" s="1">
+      <c r="B1061" s="0" t="inlineStr">
+        <is>
+          <t>Lワールドダイスター</t>
+        </is>
+      </c>
+      <c r="C1061" s="0" t="inlineStr">
+        <is>
+          <t>ワールドダイスター</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062" customFormat="1" s="1">
+      <c r="B1062" s="0" t="inlineStr">
+        <is>
+          <t>Lとんでもスキル</t>
+        </is>
+      </c>
+      <c r="C1062" s="0" t="inlineStr">
+        <is>
+          <t>とんスキ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063" customFormat="1" s="1">
+      <c r="B1063" s="0" t="inlineStr">
+        <is>
+          <t>Lとんスキ</t>
+        </is>
+      </c>
+      <c r="C1063" s="0" t="inlineStr">
+        <is>
+          <t>とんスキ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064" customFormat="1" s="1">
+      <c r="B1064" s="0" t="inlineStr">
+        <is>
+          <t>L邪神ちゃん</t>
+        </is>
+      </c>
+      <c r="C1064" s="0" t="inlineStr">
+        <is>
+          <t>邪神ちゃん</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065" customFormat="1" s="1">
+      <c r="B1065" s="0" t="inlineStr">
+        <is>
+          <t>L 新・必殺仕置人 回胴 CRASH SPEC</t>
+        </is>
+      </c>
+      <c r="C1065" s="0" t="inlineStr">
+        <is>
+          <t>必殺仕置人</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066" customFormat="1" s="1">
+      <c r="B1066" s="0" t="inlineStr">
+        <is>
+          <t>L新・必殺仕置人 回胴</t>
+        </is>
+      </c>
+      <c r="C1066" s="0" t="inlineStr">
+        <is>
+          <t>必殺仕置人</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067" customFormat="1" s="1">
+      <c r="B1067" s="0" t="inlineStr">
+        <is>
+          <t>スマスロ とある魔術の禁書目録2</t>
+        </is>
+      </c>
+      <c r="C1067" s="0" t="inlineStr">
+        <is>
+          <t>とある禁書目録2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068" customFormat="1" s="1">
+      <c r="B1068" s="0" t="inlineStr">
+        <is>
+          <t>とんでもスキルで異世界放浪メシ</t>
+        </is>
+      </c>
+      <c r="C1068" s="0" t="inlineStr">
+        <is>
+          <t>とんスキ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069" customFormat="1" s="1">
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Lインデックス2</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>とある禁書目録2</t>
+        </is>
+      </c>
+    </row>
     <row r="1070" customFormat="1" s="1"/>
     <row r="1071" customFormat="1" s="1"/>
     <row r="1072" customFormat="1" s="1"/>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1069"/>
+  <dimension ref="A1:C1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -13372,26 +13372,125 @@
       </c>
     </row>
     <row r="1069" customFormat="1" s="1">
-      <c r="B1069" t="inlineStr">
+      <c r="B1069" s="0" t="inlineStr">
         <is>
           <t>Lインデックス2</t>
         </is>
       </c>
-      <c r="C1069" t="inlineStr">
+      <c r="C1069" s="0" t="inlineStr">
         <is>
           <t>とある禁書目録2</t>
         </is>
       </c>
     </row>
-    <row r="1070" customFormat="1" s="1"/>
-    <row r="1071" customFormat="1" s="1"/>
-    <row r="1072" customFormat="1" s="1"/>
-    <row r="1073" customFormat="1" s="1"/>
-    <row r="1074" customFormat="1" s="1"/>
-    <row r="1075" customFormat="1" s="1"/>
-    <row r="1076" customFormat="1" s="1"/>
-    <row r="1077" customFormat="1" s="1"/>
-    <row r="1078" customFormat="1" s="1"/>
+    <row r="1070" customFormat="1" s="1">
+      <c r="B1070" s="0" t="inlineStr">
+        <is>
+          <t>Lストファイ6</t>
+        </is>
+      </c>
+      <c r="C1070" s="0" t="inlineStr">
+        <is>
+          <t>スト6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071" customFormat="1" s="1">
+      <c r="B1071" s="0" t="inlineStr">
+        <is>
+          <t>Lリゼロ2</t>
+        </is>
+      </c>
+      <c r="C1071" s="0" t="inlineStr">
+        <is>
+          <t>Re：ゼロ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072" customFormat="1" s="1">
+      <c r="B1072" s="0" t="inlineStr">
+        <is>
+          <t>Lパチスロ 喰霊-零-Re</t>
+        </is>
+      </c>
+      <c r="C1072" s="0" t="inlineStr">
+        <is>
+          <t>喰霊零Re</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073" customFormat="1" s="1">
+      <c r="B1073" s="0" t="inlineStr">
+        <is>
+          <t>L喰霊-零-Re</t>
+        </is>
+      </c>
+      <c r="C1073" s="0" t="inlineStr">
+        <is>
+          <t>喰霊零Re</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074" customFormat="1" s="1">
+      <c r="B1074" s="0" t="inlineStr">
+        <is>
+          <t>Lうしおととら 白面決戦</t>
+        </is>
+      </c>
+      <c r="C1074" s="0" t="inlineStr">
+        <is>
+          <t>うしおととら</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075" customFormat="1" s="1">
+      <c r="B1075" s="0" t="inlineStr">
+        <is>
+          <t>スマスロ交響詩篇エウレカセブン4 HI-EVOLUTION</t>
+        </is>
+      </c>
+      <c r="C1075" s="0" t="inlineStr">
+        <is>
+          <t>エウレカ4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076" customFormat="1" s="1">
+      <c r="B1076" s="0" t="inlineStr">
+        <is>
+          <t>L交響詩篇エウレカセブン4</t>
+        </is>
+      </c>
+      <c r="C1076" s="0" t="inlineStr">
+        <is>
+          <t>エウレカ4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077" customFormat="1" s="1">
+      <c r="B1077" s="0" t="inlineStr">
+        <is>
+          <t>Lバイオハザード ヴィレッジ</t>
+        </is>
+      </c>
+      <c r="C1077" s="0" t="inlineStr">
+        <is>
+          <t>バイオヴィレッジ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078" customFormat="1" s="1">
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>スマスロ バイオハザード ヴィレッジ</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>バイオヴィレッジ</t>
+        </is>
+      </c>
+    </row>
     <row r="1079" customFormat="1" s="1"/>
     <row r="1080" customFormat="1" s="1"/>
     <row r="1081" customFormat="1" s="1"/>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1078"/>
+  <dimension ref="A1:C1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -13480,27 +13480,137 @@
       </c>
     </row>
     <row r="1078" customFormat="1" s="1">
-      <c r="B1078" t="inlineStr">
+      <c r="B1078" s="0" t="inlineStr">
         <is>
           <t>スマスロ バイオハザード ヴィレッジ</t>
         </is>
       </c>
-      <c r="C1078" t="inlineStr">
+      <c r="C1078" s="0" t="inlineStr">
         <is>
           <t>バイオヴィレッジ</t>
         </is>
       </c>
     </row>
-    <row r="1079" customFormat="1" s="1"/>
-    <row r="1080" customFormat="1" s="1"/>
-    <row r="1081" customFormat="1" s="1"/>
-    <row r="1082" customFormat="1" s="1"/>
-    <row r="1083" customFormat="1" s="1"/>
-    <row r="1084" customFormat="1" s="1"/>
-    <row r="1085" customFormat="1" s="1"/>
-    <row r="1086" customFormat="1" s="1"/>
-    <row r="1087" customFormat="1" s="1"/>
-    <row r="1088" customFormat="1" s="1"/>
+    <row r="1079" customFormat="1" s="1">
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>スマスロ リコリス・リコイル</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>リコリス</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080" customFormat="1" s="1">
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>L青春ブタ野郎はバニーガール先輩の夢を見ない</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>青ブタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081" customFormat="1" s="1">
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Lパチスロ 彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>かのかり</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082" customFormat="1" s="1">
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>モグモグ風林火山 大海戦の巻</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>モグモグ大海戦</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083" customFormat="1" s="1">
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>スマスロ タコスロ</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>タコスロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084" customFormat="1" s="1">
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Lリコリス・リコイル</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>リコリス</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085" customFormat="1" s="1">
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>L青春ブタ野郎はバニーガール</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>青ブタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086" customFormat="1" s="1">
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>L彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>かのかり</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087" customFormat="1" s="1">
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Lモグモグ風林火山</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>モグモグ大海戦</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088" customFormat="1" s="1">
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>LBタコスロ</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>タコスロ</t>
+        </is>
+      </c>
+    </row>
     <row r="1089" customFormat="1" s="1"/>
     <row r="1090" customFormat="1" s="1"/>
     <row r="1091" customFormat="1" s="1"/>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1088"/>
+  <dimension ref="A1:C1089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -13492,126 +13492,137 @@
       </c>
     </row>
     <row r="1079" customFormat="1" s="1">
-      <c r="B1079" t="inlineStr">
+      <c r="B1079" s="0" t="inlineStr">
         <is>
           <t>スマスロ リコリス・リコイル</t>
         </is>
       </c>
-      <c r="C1079" t="inlineStr">
+      <c r="C1079" s="0" t="inlineStr">
         <is>
           <t>リコリス</t>
         </is>
       </c>
     </row>
     <row r="1080" customFormat="1" s="1">
-      <c r="B1080" t="inlineStr">
+      <c r="B1080" s="0" t="inlineStr">
         <is>
           <t>L青春ブタ野郎はバニーガール先輩の夢を見ない</t>
         </is>
       </c>
-      <c r="C1080" t="inlineStr">
+      <c r="C1080" s="0" t="inlineStr">
         <is>
           <t>青ブタ</t>
         </is>
       </c>
     </row>
     <row r="1081" customFormat="1" s="1">
-      <c r="B1081" t="inlineStr">
+      <c r="B1081" s="0" t="inlineStr">
         <is>
           <t>Lパチスロ 彼女、お借りします</t>
         </is>
       </c>
-      <c r="C1081" t="inlineStr">
+      <c r="C1081" s="0" t="inlineStr">
         <is>
           <t>かのかり</t>
         </is>
       </c>
     </row>
     <row r="1082" customFormat="1" s="1">
-      <c r="B1082" t="inlineStr">
+      <c r="B1082" s="0" t="inlineStr">
         <is>
           <t>モグモグ風林火山 大海戦の巻</t>
         </is>
       </c>
-      <c r="C1082" t="inlineStr">
+      <c r="C1082" s="0" t="inlineStr">
         <is>
           <t>モグモグ大海戦</t>
         </is>
       </c>
     </row>
     <row r="1083" customFormat="1" s="1">
-      <c r="B1083" t="inlineStr">
+      <c r="B1083" s="0" t="inlineStr">
         <is>
           <t>スマスロ タコスロ</t>
         </is>
       </c>
-      <c r="C1083" t="inlineStr">
+      <c r="C1083" s="0" t="inlineStr">
         <is>
           <t>タコスロ</t>
         </is>
       </c>
     </row>
     <row r="1084" customFormat="1" s="1">
-      <c r="B1084" t="inlineStr">
+      <c r="B1084" s="0" t="inlineStr">
         <is>
           <t>Lリコリス・リコイル</t>
         </is>
       </c>
-      <c r="C1084" t="inlineStr">
+      <c r="C1084" s="0" t="inlineStr">
         <is>
           <t>リコリス</t>
         </is>
       </c>
     </row>
     <row r="1085" customFormat="1" s="1">
-      <c r="B1085" t="inlineStr">
+      <c r="B1085" s="0" t="inlineStr">
         <is>
           <t>L青春ブタ野郎はバニーガール</t>
         </is>
       </c>
-      <c r="C1085" t="inlineStr">
+      <c r="C1085" s="0" t="inlineStr">
         <is>
           <t>青ブタ</t>
         </is>
       </c>
     </row>
     <row r="1086" customFormat="1" s="1">
-      <c r="B1086" t="inlineStr">
+      <c r="B1086" s="0" t="inlineStr">
         <is>
           <t>L彼女、お借りします</t>
         </is>
       </c>
-      <c r="C1086" t="inlineStr">
+      <c r="C1086" s="0" t="inlineStr">
         <is>
           <t>かのかり</t>
         </is>
       </c>
     </row>
     <row r="1087" customFormat="1" s="1">
-      <c r="B1087" t="inlineStr">
+      <c r="B1087" s="0" t="inlineStr">
         <is>
           <t>Lモグモグ風林火山</t>
         </is>
       </c>
-      <c r="C1087" t="inlineStr">
+      <c r="C1087" s="0" t="inlineStr">
         <is>
           <t>モグモグ大海戦</t>
         </is>
       </c>
     </row>
     <row r="1088" customFormat="1" s="1">
-      <c r="B1088" t="inlineStr">
+      <c r="B1088" s="0" t="inlineStr">
         <is>
           <t>LBタコスロ</t>
         </is>
       </c>
-      <c r="C1088" t="inlineStr">
+      <c r="C1088" s="0" t="inlineStr">
         <is>
           <t>タコスロ</t>
         </is>
       </c>
     </row>
-    <row r="1089" customFormat="1" s="1"/>
+    <row r="1089" customFormat="1" s="1">
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>L青春ブタ野郎バニーガール先輩</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>青ブタ</t>
+        </is>
+      </c>
+    </row>
     <row r="1090" customFormat="1" s="1"/>
     <row r="1091" customFormat="1" s="1"/>
     <row r="1092" customFormat="1" s="1"/>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1089"/>
+  <dimension ref="A1:C1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -13612,19 +13612,41 @@
       </c>
     </row>
     <row r="1089" customFormat="1" s="1">
-      <c r="B1089" t="inlineStr">
+      <c r="B1089" s="0" t="inlineStr">
         <is>
           <t>L青春ブタ野郎バニーガール先輩</t>
         </is>
       </c>
-      <c r="C1089" t="inlineStr">
+      <c r="C1089" s="0" t="inlineStr">
         <is>
           <t>青ブタ</t>
         </is>
       </c>
     </row>
-    <row r="1090" customFormat="1" s="1"/>
-    <row r="1091" customFormat="1" s="1"/>
+    <row r="1090" customFormat="1" s="1">
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>パチスロ見える子ちゃん</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>見える子ちゃん</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091" customFormat="1" s="1">
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>L見える子ちゃん</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>見える子ちゃん</t>
+        </is>
+      </c>
+    </row>
     <row r="1092" customFormat="1" s="1"/>
     <row r="1093" customFormat="1" s="1"/>
     <row r="1094" customFormat="1" s="1"/>

--- a/機種名変換.xlsx
+++ b/機種名変換.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1091"/>
+  <dimension ref="A1:C1094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -13624,32 +13624,65 @@
       </c>
     </row>
     <row r="1090" customFormat="1" s="1">
-      <c r="B1090" t="inlineStr">
+      <c r="B1090" s="0" t="inlineStr">
         <is>
           <t>パチスロ見える子ちゃん</t>
         </is>
       </c>
-      <c r="C1090" t="inlineStr">
+      <c r="C1090" s="0" t="inlineStr">
         <is>
           <t>見える子ちゃん</t>
         </is>
       </c>
     </row>
     <row r="1091" customFormat="1" s="1">
-      <c r="B1091" t="inlineStr">
+      <c r="B1091" s="0" t="inlineStr">
         <is>
           <t>L見える子ちゃん</t>
         </is>
       </c>
-      <c r="C1091" t="inlineStr">
+      <c r="C1091" s="0" t="inlineStr">
         <is>
           <t>見える子ちゃん</t>
         </is>
       </c>
     </row>
-    <row r="1092" customFormat="1" s="1"/>
-    <row r="1093" customFormat="1" s="1"/>
-    <row r="1094" customFormat="1" s="1"/>
+    <row r="1092" customFormat="1" s="1">
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Lタコスロ</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>タコスロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093" customFormat="1" s="1">
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Lモグモグ風林火山 大海戦の巻</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>モグモグ大海戦</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094" customFormat="1" s="1">
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>L青ブタ</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>青ブタ</t>
+        </is>
+      </c>
+    </row>
     <row r="1095" customFormat="1" s="1"/>
     <row r="1096" customFormat="1" s="1"/>
     <row r="1097" customFormat="1" s="1"/>
